--- a/Data/EXCEL/Transfer/salemon/202206/6652-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/6652-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BBC1388F-A1BB-4964-A77D-DBEA9C637FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB306288-C8BC-41BD-B6CB-100623935D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="6652-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="18">
   <si>
     <t>月別</t>
   </si>
@@ -1218,20 +1218,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q62"/>
+  <dimension ref="A1:Q63"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.875" customWidth="1"/>
-    <col min="2" max="6" width="10.875" customWidth="1"/>
-    <col min="7" max="7" width="11.875" customWidth="1"/>
-    <col min="8" max="8" width="12.375" customWidth="1"/>
-    <col min="9" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="10.25" customWidth="1"/>
-    <col min="13" max="13" width="12.375" customWidth="1"/>
-    <col min="14" max="15" width="10.25" customWidth="1"/>
-    <col min="16" max="16" width="12.375" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="14.125" customWidth="1"/>
+    <col min="2" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="9" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="13.5" customWidth="1"/>
+    <col min="12" max="12" width="11.25" customWidth="1"/>
+    <col min="13" max="13" width="13.5" customWidth="1"/>
+    <col min="14" max="15" width="11.25" customWidth="1"/>
+    <col min="16" max="16" width="13.5" customWidth="1"/>
+    <col min="17" max="17" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1384,25 +1384,25 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
       <c r="C5" s="7">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="D5" s="7">
-        <v>9.25</v>
+        <v>9.09</v>
       </c>
       <c r="E5" s="7">
-        <v>8.08</v>
+        <v>7.9</v>
       </c>
       <c r="F5" s="8">
-        <v>-0.65</v>
+        <v>-0.5</v>
       </c>
       <c r="G5" s="8">
-        <v>-7.1</v>
+        <v>-5.88</v>
       </c>
       <c r="H5" s="9">
         <v>0</v>
@@ -1437,25 +1437,25 @@
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>9.7200000000000006</v>
+        <v>9.15</v>
       </c>
       <c r="C6" s="7">
-        <v>9.15</v>
+        <v>8.5</v>
       </c>
       <c r="D6" s="7">
-        <v>9.89</v>
+        <v>9.25</v>
       </c>
       <c r="E6" s="7">
-        <v>8.75</v>
+        <v>8.08</v>
       </c>
       <c r="F6" s="8">
-        <v>-0.56999999999999995</v>
+        <v>-0.65</v>
       </c>
       <c r="G6" s="8">
-        <v>-5.86</v>
+        <v>-7.1</v>
       </c>
       <c r="H6" s="9">
         <v>0</v>
@@ -1490,25 +1490,25 @@
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>12.1</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="C7" s="7">
-        <v>9.7200000000000006</v>
+        <v>9.15</v>
       </c>
       <c r="D7" s="7">
-        <v>12.5</v>
+        <v>9.89</v>
       </c>
       <c r="E7" s="7">
-        <v>8.6999999999999993</v>
+        <v>8.75</v>
       </c>
       <c r="F7" s="8">
-        <v>-2.38</v>
+        <v>-0.56999999999999995</v>
       </c>
       <c r="G7" s="8">
-        <v>-19.670000000000002</v>
+        <v>-5.86</v>
       </c>
       <c r="H7" s="9">
         <v>0</v>
@@ -1543,25 +1543,25 @@
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="C8" s="7">
-        <v>12.1</v>
+        <v>9.7200000000000006</v>
       </c>
       <c r="D8" s="7">
-        <v>13.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" s="7">
-        <v>11.5</v>
-      </c>
-      <c r="F8" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>0.83</v>
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="F8" s="8">
+        <v>-2.38</v>
+      </c>
+      <c r="G8" s="8">
+        <v>-19.670000000000002</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -1596,25 +1596,25 @@
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="C9" s="7">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="D9" s="7">
-        <v>15.65</v>
+        <v>13.8</v>
       </c>
       <c r="E9" s="7">
-        <v>12</v>
-      </c>
-      <c r="F9" s="8">
-        <v>-2.8</v>
-      </c>
-      <c r="G9" s="8">
-        <v>-18.920000000000002</v>
+        <v>11.5</v>
+      </c>
+      <c r="F9" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0.83</v>
       </c>
       <c r="H9" s="9">
         <v>0</v>
@@ -1649,25 +1649,25 @@
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>12.65</v>
+        <v>14.8</v>
       </c>
       <c r="C10" s="7">
-        <v>14.8</v>
+        <v>12</v>
       </c>
       <c r="D10" s="7">
-        <v>16.8</v>
+        <v>15.65</v>
       </c>
       <c r="E10" s="7">
-        <v>12.65</v>
-      </c>
-      <c r="F10" s="10">
-        <v>2.15</v>
-      </c>
-      <c r="G10" s="10">
-        <v>17</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="8">
+        <v>-2.8</v>
+      </c>
+      <c r="G10" s="8">
+        <v>-18.920000000000002</v>
       </c>
       <c r="H10" s="9">
         <v>0</v>
@@ -1702,25 +1702,25 @@
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>12.95</v>
+        <v>12.65</v>
       </c>
       <c r="C11" s="7">
+        <v>14.8</v>
+      </c>
+      <c r="D11" s="7">
+        <v>16.8</v>
+      </c>
+      <c r="E11" s="7">
         <v>12.65</v>
       </c>
-      <c r="D11" s="7">
-        <v>13.5</v>
-      </c>
-      <c r="E11" s="7">
-        <v>11.8</v>
-      </c>
-      <c r="F11" s="8">
-        <v>-0.3</v>
-      </c>
-      <c r="G11" s="8">
-        <v>-2.3199999999999998</v>
+      <c r="F11" s="10">
+        <v>2.15</v>
+      </c>
+      <c r="G11" s="10">
+        <v>17</v>
       </c>
       <c r="H11" s="9">
         <v>0</v>
@@ -1755,25 +1755,25 @@
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
+        <v>44501</v>
       </c>
       <c r="B12" s="7">
-        <v>14.75</v>
+        <v>12.95</v>
       </c>
       <c r="C12" s="7">
-        <v>12.95</v>
+        <v>12.65</v>
       </c>
       <c r="D12" s="7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="E12" s="7">
-        <v>12.25</v>
+        <v>11.8</v>
       </c>
       <c r="F12" s="8">
-        <v>-1.8</v>
+        <v>-0.3</v>
       </c>
       <c r="G12" s="8">
-        <v>-12.2</v>
+        <v>-2.3199999999999998</v>
       </c>
       <c r="H12" s="9">
         <v>0</v>
@@ -1808,25 +1808,25 @@
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7">
-        <v>13.6</v>
+        <v>14.75</v>
       </c>
       <c r="C13" s="7">
-        <v>14.75</v>
+        <v>12.95</v>
       </c>
       <c r="D13" s="7">
-        <v>16.7</v>
+        <v>15</v>
       </c>
       <c r="E13" s="7">
-        <v>13.55</v>
-      </c>
-      <c r="F13" s="10">
-        <v>1.1499999999999999</v>
-      </c>
-      <c r="G13" s="10">
-        <v>8.4600000000000009</v>
+        <v>12.25</v>
+      </c>
+      <c r="F13" s="8">
+        <v>-1.8</v>
+      </c>
+      <c r="G13" s="8">
+        <v>-12.2</v>
       </c>
       <c r="H13" s="9">
         <v>0</v>
@@ -1861,25 +1861,25 @@
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7">
-        <v>15.9</v>
+        <v>13.6</v>
       </c>
       <c r="C14" s="7">
-        <v>13.6</v>
+        <v>14.75</v>
       </c>
       <c r="D14" s="7">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E14" s="7">
-        <v>13.35</v>
-      </c>
-      <c r="F14" s="8">
-        <v>-2.2999999999999998</v>
-      </c>
-      <c r="G14" s="8">
-        <v>-14.47</v>
+        <v>13.55</v>
+      </c>
+      <c r="F14" s="10">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="G14" s="10">
+        <v>8.4600000000000009</v>
       </c>
       <c r="H14" s="9">
         <v>0</v>
@@ -1914,25 +1914,25 @@
     </row>
     <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>44378</v>
+        <v>44409</v>
       </c>
       <c r="B15" s="7">
-        <v>20.6</v>
+        <v>15.9</v>
       </c>
       <c r="C15" s="7">
-        <v>15.9</v>
+        <v>13.6</v>
       </c>
       <c r="D15" s="7">
-        <v>20.8</v>
+        <v>17.8</v>
       </c>
       <c r="E15" s="7">
-        <v>15.05</v>
+        <v>13.35</v>
       </c>
       <c r="F15" s="8">
-        <v>-4.7</v>
+        <v>-2.2999999999999998</v>
       </c>
       <c r="G15" s="8">
-        <v>-22.82</v>
+        <v>-14.47</v>
       </c>
       <c r="H15" s="9">
         <v>0</v>
@@ -1967,25 +1967,25 @@
     </row>
     <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>44348</v>
+        <v>44378</v>
       </c>
       <c r="B16" s="7">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="C16" s="7">
-        <v>20.6</v>
+        <v>15.9</v>
       </c>
       <c r="D16" s="7">
-        <v>23.5</v>
+        <v>20.8</v>
       </c>
       <c r="E16" s="7">
-        <v>20.05</v>
+        <v>15.05</v>
       </c>
       <c r="F16" s="8">
-        <v>-2.9</v>
+        <v>-4.7</v>
       </c>
       <c r="G16" s="8">
-        <v>-12.34</v>
+        <v>-22.82</v>
       </c>
       <c r="H16" s="9">
         <v>0</v>
@@ -2020,25 +2020,25 @@
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>44317</v>
+        <v>44348</v>
       </c>
       <c r="B17" s="7">
-        <v>24.85</v>
+        <v>23.5</v>
       </c>
       <c r="C17" s="7">
+        <v>20.6</v>
+      </c>
+      <c r="D17" s="7">
         <v>23.5</v>
       </c>
-      <c r="D17" s="7">
-        <v>25.45</v>
-      </c>
       <c r="E17" s="7">
-        <v>22.3</v>
+        <v>20.05</v>
       </c>
       <c r="F17" s="8">
-        <v>-1.35</v>
+        <v>-2.9</v>
       </c>
       <c r="G17" s="8">
-        <v>-5.43</v>
+        <v>-12.34</v>
       </c>
       <c r="H17" s="9">
         <v>0</v>
@@ -2073,25 +2073,25 @@
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>44287</v>
+        <v>44317</v>
       </c>
       <c r="B18" s="7">
-        <v>24.75</v>
+        <v>24.85</v>
       </c>
       <c r="C18" s="7">
-        <v>24.85</v>
+        <v>23.5</v>
       </c>
       <c r="D18" s="7">
-        <v>27</v>
+        <v>25.45</v>
       </c>
       <c r="E18" s="7">
-        <v>24.75</v>
-      </c>
-      <c r="F18" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="G18" s="10">
-        <v>0.4</v>
+        <v>22.3</v>
+      </c>
+      <c r="F18" s="8">
+        <v>-1.35</v>
+      </c>
+      <c r="G18" s="8">
+        <v>-5.43</v>
       </c>
       <c r="H18" s="9">
         <v>0</v>
@@ -2126,25 +2126,25 @@
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>44256</v>
+        <v>44287</v>
       </c>
       <c r="B19" s="7">
-        <v>24.95</v>
+        <v>24.75</v>
       </c>
       <c r="C19" s="7">
+        <v>24.85</v>
+      </c>
+      <c r="D19" s="7">
+        <v>27</v>
+      </c>
+      <c r="E19" s="7">
         <v>24.75</v>
       </c>
-      <c r="D19" s="7">
-        <v>27.5</v>
-      </c>
-      <c r="E19" s="7">
-        <v>24.45</v>
-      </c>
-      <c r="F19" s="8">
-        <v>-0.2</v>
-      </c>
-      <c r="G19" s="8">
-        <v>-0.8</v>
+      <c r="F19" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="G19" s="10">
+        <v>0.4</v>
       </c>
       <c r="H19" s="9">
         <v>0</v>
@@ -2179,25 +2179,25 @@
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>44228</v>
+        <v>44256</v>
       </c>
       <c r="B20" s="7">
-        <v>24.65</v>
+        <v>24.95</v>
       </c>
       <c r="C20" s="7">
-        <v>24.95</v>
+        <v>24.75</v>
       </c>
       <c r="D20" s="7">
-        <v>25.25</v>
+        <v>27.5</v>
       </c>
       <c r="E20" s="7">
-        <v>24.5</v>
-      </c>
-      <c r="F20" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G20" s="10">
-        <v>1.22</v>
+        <v>24.45</v>
+      </c>
+      <c r="F20" s="8">
+        <v>-0.2</v>
+      </c>
+      <c r="G20" s="8">
+        <v>-0.8</v>
       </c>
       <c r="H20" s="9">
         <v>0</v>
@@ -2232,25 +2232,25 @@
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>44197</v>
+        <v>44228</v>
       </c>
       <c r="B21" s="7">
+        <v>24.65</v>
+      </c>
+      <c r="C21" s="7">
+        <v>24.95</v>
+      </c>
+      <c r="D21" s="7">
         <v>25.25</v>
       </c>
-      <c r="C21" s="7">
-        <v>24.65</v>
-      </c>
-      <c r="D21" s="7">
-        <v>26.35</v>
-      </c>
       <c r="E21" s="7">
-        <v>24.65</v>
-      </c>
-      <c r="F21" s="8">
-        <v>-0.6</v>
-      </c>
-      <c r="G21" s="8">
-        <v>-2.38</v>
+        <v>24.5</v>
+      </c>
+      <c r="F21" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G21" s="10">
+        <v>1.22</v>
       </c>
       <c r="H21" s="9">
         <v>0</v>
@@ -2285,25 +2285,25 @@
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>44166</v>
+        <v>44197</v>
       </c>
       <c r="B22" s="7">
-        <v>27.75</v>
+        <v>25.25</v>
       </c>
       <c r="C22" s="7">
-        <v>25.25</v>
+        <v>24.65</v>
       </c>
       <c r="D22" s="7">
-        <v>28</v>
+        <v>26.35</v>
       </c>
       <c r="E22" s="7">
-        <v>24.3</v>
+        <v>24.65</v>
       </c>
       <c r="F22" s="8">
-        <v>-2.5</v>
+        <v>-0.6</v>
       </c>
       <c r="G22" s="8">
-        <v>-9.01</v>
+        <v>-2.38</v>
       </c>
       <c r="H22" s="9">
         <v>0</v>
@@ -2338,25 +2338,25 @@
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>44136</v>
+        <v>44166</v>
       </c>
       <c r="B23" s="7">
-        <v>27.1</v>
+        <v>27.75</v>
       </c>
       <c r="C23" s="7">
-        <v>27.75</v>
+        <v>25.25</v>
       </c>
       <c r="D23" s="7">
-        <v>29.2</v>
+        <v>28</v>
       </c>
       <c r="E23" s="7">
-        <v>26.8</v>
-      </c>
-      <c r="F23" s="10">
-        <v>0.65</v>
-      </c>
-      <c r="G23" s="10">
-        <v>2.4</v>
+        <v>24.3</v>
+      </c>
+      <c r="F23" s="8">
+        <v>-2.5</v>
+      </c>
+      <c r="G23" s="8">
+        <v>-9.01</v>
       </c>
       <c r="H23" s="9">
         <v>0</v>
@@ -2391,25 +2391,25 @@
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>44105</v>
+        <v>44136</v>
       </c>
       <c r="B24" s="7">
-        <v>25.2</v>
+        <v>27.1</v>
       </c>
       <c r="C24" s="7">
-        <v>27.1</v>
+        <v>27.75</v>
       </c>
       <c r="D24" s="7">
-        <v>28.35</v>
+        <v>29.2</v>
       </c>
       <c r="E24" s="7">
-        <v>24</v>
+        <v>26.8</v>
       </c>
       <c r="F24" s="10">
-        <v>1.9</v>
+        <v>0.65</v>
       </c>
       <c r="G24" s="10">
-        <v>7.54</v>
+        <v>2.4</v>
       </c>
       <c r="H24" s="9">
         <v>0</v>
@@ -2444,25 +2444,25 @@
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
-        <v>44075</v>
+        <v>44105</v>
       </c>
       <c r="B25" s="7">
-        <v>28.2</v>
+        <v>25.2</v>
       </c>
       <c r="C25" s="7">
-        <v>25.2</v>
+        <v>27.1</v>
       </c>
       <c r="D25" s="7">
-        <v>29.1</v>
+        <v>28.35</v>
       </c>
       <c r="E25" s="7">
         <v>24</v>
       </c>
-      <c r="F25" s="8">
-        <v>-3</v>
-      </c>
-      <c r="G25" s="8">
-        <v>-10.64</v>
+      <c r="F25" s="10">
+        <v>1.9</v>
+      </c>
+      <c r="G25" s="10">
+        <v>7.54</v>
       </c>
       <c r="H25" s="9">
         <v>0</v>
@@ -2497,25 +2497,25 @@
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
-        <v>44044</v>
+        <v>44075</v>
       </c>
       <c r="B26" s="7">
-        <v>30.05</v>
+        <v>28.2</v>
       </c>
       <c r="C26" s="7">
-        <v>28.2</v>
+        <v>25.2</v>
       </c>
       <c r="D26" s="7">
-        <v>34</v>
+        <v>29.1</v>
       </c>
       <c r="E26" s="7">
-        <v>28.2</v>
+        <v>24</v>
       </c>
       <c r="F26" s="8">
-        <v>-1.85</v>
+        <v>-3</v>
       </c>
       <c r="G26" s="8">
-        <v>-6.16</v>
+        <v>-10.64</v>
       </c>
       <c r="H26" s="9">
         <v>0</v>
@@ -2550,25 +2550,25 @@
     </row>
     <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
-        <v>44013</v>
+        <v>44044</v>
       </c>
       <c r="B27" s="7">
-        <v>19.5</v>
+        <v>30.05</v>
       </c>
       <c r="C27" s="7">
-        <v>30.05</v>
+        <v>28.2</v>
       </c>
       <c r="D27" s="7">
-        <v>37.450000000000003</v>
+        <v>34</v>
       </c>
       <c r="E27" s="7">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="F27" s="10">
-        <v>10.55</v>
-      </c>
-      <c r="G27" s="10">
-        <v>54.1</v>
+        <v>28.2</v>
+      </c>
+      <c r="F27" s="8">
+        <v>-1.85</v>
+      </c>
+      <c r="G27" s="8">
+        <v>-6.16</v>
       </c>
       <c r="H27" s="9">
         <v>0</v>
@@ -2603,25 +2603,25 @@
     </row>
     <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
-        <v>43983</v>
+        <v>44013</v>
       </c>
       <c r="B28" s="7">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="C28" s="7">
-        <v>19.5</v>
+        <v>30.05</v>
       </c>
       <c r="D28" s="7">
-        <v>20.2</v>
+        <v>37.450000000000003</v>
       </c>
       <c r="E28" s="7">
-        <v>15.2</v>
+        <v>19.600000000000001</v>
       </c>
       <c r="F28" s="10">
-        <v>2.2999999999999998</v>
+        <v>10.55</v>
       </c>
       <c r="G28" s="10">
-        <v>13.37</v>
+        <v>54.1</v>
       </c>
       <c r="H28" s="9">
         <v>0</v>
@@ -2656,25 +2656,25 @@
     </row>
     <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
-        <v>43952</v>
+        <v>43983</v>
       </c>
       <c r="B29" s="7">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="C29" s="7">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="D29" s="7">
-        <v>19.850000000000001</v>
+        <v>20.2</v>
       </c>
       <c r="E29" s="7">
-        <v>16.149999999999999</v>
-      </c>
-      <c r="F29" s="8">
-        <v>-0.8</v>
-      </c>
-      <c r="G29" s="8">
-        <v>-4.4400000000000004</v>
+        <v>15.2</v>
+      </c>
+      <c r="F29" s="10">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G29" s="10">
+        <v>13.37</v>
       </c>
       <c r="H29" s="9">
         <v>0</v>
@@ -2709,25 +2709,25 @@
     </row>
     <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
-        <v>43922</v>
+        <v>43952</v>
       </c>
       <c r="B30" s="7">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="C30" s="7">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="D30" s="7">
-        <v>18.850000000000001</v>
+        <v>19.850000000000001</v>
       </c>
       <c r="E30" s="7">
-        <v>16</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1.75</v>
-      </c>
-      <c r="G30" s="10">
-        <v>10.77</v>
+        <v>16.149999999999999</v>
+      </c>
+      <c r="F30" s="8">
+        <v>-0.8</v>
+      </c>
+      <c r="G30" s="8">
+        <v>-4.4400000000000004</v>
       </c>
       <c r="H30" s="9">
         <v>0</v>
@@ -2762,25 +2762,25 @@
     </row>
     <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
-        <v>43891</v>
+        <v>43922</v>
       </c>
       <c r="B31" s="7">
-        <v>19.7</v>
+        <v>16.25</v>
       </c>
       <c r="C31" s="7">
-        <v>16.25</v>
+        <v>18</v>
       </c>
       <c r="D31" s="7">
-        <v>20.49</v>
+        <v>18.850000000000001</v>
       </c>
       <c r="E31" s="7">
-        <v>15.45</v>
-      </c>
-      <c r="F31" s="8">
-        <v>-3.45</v>
-      </c>
-      <c r="G31" s="8">
-        <v>-17.510000000000002</v>
+        <v>16</v>
+      </c>
+      <c r="F31" s="10">
+        <v>1.75</v>
+      </c>
+      <c r="G31" s="10">
+        <v>10.77</v>
       </c>
       <c r="H31" s="9">
         <v>0</v>
@@ -2815,25 +2815,25 @@
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
-        <v>43862</v>
+        <v>43891</v>
       </c>
       <c r="B32" s="7">
-        <v>20.100000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="C32" s="7">
-        <v>19.7</v>
+        <v>16.25</v>
       </c>
       <c r="D32" s="7">
-        <v>20.65</v>
+        <v>20.49</v>
       </c>
       <c r="E32" s="7">
-        <v>19</v>
+        <v>15.45</v>
       </c>
       <c r="F32" s="8">
-        <v>-0.4</v>
+        <v>-3.45</v>
       </c>
       <c r="G32" s="8">
-        <v>-1.99</v>
+        <v>-17.510000000000002</v>
       </c>
       <c r="H32" s="9">
         <v>0</v>
@@ -2868,25 +2868,25 @@
     </row>
     <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
-        <v>43831</v>
+        <v>43862</v>
       </c>
       <c r="B33" s="7">
-        <v>19.55</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="C33" s="7">
-        <v>20.100000000000001</v>
+        <v>19.7</v>
       </c>
       <c r="D33" s="7">
-        <v>20.93</v>
+        <v>20.65</v>
       </c>
       <c r="E33" s="7">
-        <v>19.3</v>
-      </c>
-      <c r="F33" s="10">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="G33" s="10">
-        <v>2.81</v>
+        <v>19</v>
+      </c>
+      <c r="F33" s="8">
+        <v>-0.4</v>
+      </c>
+      <c r="G33" s="8">
+        <v>-1.99</v>
       </c>
       <c r="H33" s="9">
         <v>0</v>
@@ -2921,25 +2921,25 @@
     </row>
     <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
-        <v>43800</v>
+        <v>43831</v>
       </c>
       <c r="B34" s="7">
-        <v>20</v>
+        <v>19.55</v>
       </c>
       <c r="C34" s="7">
-        <v>19.55</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D34" s="7">
-        <v>20.3</v>
+        <v>20.93</v>
       </c>
       <c r="E34" s="7">
-        <v>19.02</v>
-      </c>
-      <c r="F34" s="8">
-        <v>-0.45</v>
-      </c>
-      <c r="G34" s="8">
-        <v>-2.25</v>
+        <v>19.3</v>
+      </c>
+      <c r="F34" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="G34" s="10">
+        <v>2.81</v>
       </c>
       <c r="H34" s="9">
         <v>0</v>
@@ -2953,8 +2953,8 @@
       <c r="K34" s="9">
         <v>0</v>
       </c>
-      <c r="L34" s="8">
-        <v>-100</v>
+      <c r="L34" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M34" s="9">
         <v>0</v>
@@ -2968,31 +2968,31 @@
       <c r="P34" s="9">
         <v>0</v>
       </c>
-      <c r="Q34" s="8">
-        <v>-100</v>
+      <c r="Q34" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
-        <v>43770</v>
+        <v>43800</v>
       </c>
       <c r="B35" s="7">
-        <v>20.350000000000001</v>
+        <v>20</v>
       </c>
       <c r="C35" s="7">
-        <v>20</v>
+        <v>19.55</v>
       </c>
       <c r="D35" s="7">
-        <v>20.69</v>
+        <v>20.3</v>
       </c>
       <c r="E35" s="7">
-        <v>19.399999999999999</v>
+        <v>19.02</v>
       </c>
       <c r="F35" s="8">
-        <v>-0.35</v>
+        <v>-0.45</v>
       </c>
       <c r="G35" s="8">
-        <v>-1.72</v>
+        <v>-2.25</v>
       </c>
       <c r="H35" s="9">
         <v>0</v>
@@ -3027,25 +3027,25 @@
     </row>
     <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
-        <v>43739</v>
+        <v>43770</v>
       </c>
       <c r="B36" s="7">
-        <v>20.010000000000002</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="C36" s="7">
-        <v>20.350000000000001</v>
+        <v>20</v>
       </c>
       <c r="D36" s="7">
-        <v>21.19</v>
+        <v>20.69</v>
       </c>
       <c r="E36" s="7">
-        <v>20</v>
-      </c>
-      <c r="F36" s="10">
-        <v>0.34</v>
-      </c>
-      <c r="G36" s="10">
-        <v>1.7</v>
+        <v>19.399999999999999</v>
+      </c>
+      <c r="F36" s="8">
+        <v>-0.35</v>
+      </c>
+      <c r="G36" s="8">
+        <v>-1.72</v>
       </c>
       <c r="H36" s="9">
         <v>0</v>
@@ -3080,25 +3080,25 @@
     </row>
     <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
-        <v>43709</v>
+        <v>43739</v>
       </c>
       <c r="B37" s="7">
-        <v>21.85</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="C37" s="7">
-        <v>20.010000000000002</v>
+        <v>20.350000000000001</v>
       </c>
       <c r="D37" s="7">
-        <v>21.8</v>
+        <v>21.19</v>
       </c>
       <c r="E37" s="7">
         <v>20</v>
       </c>
-      <c r="F37" s="8">
-        <v>-1.84</v>
-      </c>
-      <c r="G37" s="8">
-        <v>-8.42</v>
+      <c r="F37" s="10">
+        <v>0.34</v>
+      </c>
+      <c r="G37" s="10">
+        <v>1.7</v>
       </c>
       <c r="H37" s="9">
         <v>0</v>
@@ -3133,25 +3133,25 @@
     </row>
     <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
-        <v>43678</v>
+        <v>43709</v>
       </c>
       <c r="B38" s="7">
-        <v>21.31</v>
+        <v>21.85</v>
       </c>
       <c r="C38" s="7">
-        <v>21.85</v>
+        <v>20.010000000000002</v>
       </c>
       <c r="D38" s="7">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="E38" s="7">
-        <v>20.22</v>
-      </c>
-      <c r="F38" s="10">
-        <v>0.54</v>
-      </c>
-      <c r="G38" s="10">
-        <v>2.5299999999999998</v>
+        <v>20</v>
+      </c>
+      <c r="F38" s="8">
+        <v>-1.84</v>
+      </c>
+      <c r="G38" s="8">
+        <v>-8.42</v>
       </c>
       <c r="H38" s="9">
         <v>0</v>
@@ -3186,25 +3186,25 @@
     </row>
     <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
-        <v>43647</v>
+        <v>43678</v>
       </c>
       <c r="B39" s="7">
+        <v>21.31</v>
+      </c>
+      <c r="C39" s="7">
+        <v>21.85</v>
+      </c>
+      <c r="D39" s="7">
+        <v>22</v>
+      </c>
+      <c r="E39" s="7">
         <v>20.22</v>
       </c>
-      <c r="C39" s="7">
-        <v>21.31</v>
-      </c>
-      <c r="D39" s="7">
-        <v>24</v>
-      </c>
-      <c r="E39" s="7">
-        <v>20.010000000000002</v>
-      </c>
       <c r="F39" s="10">
-        <v>1.0900000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="G39" s="10">
-        <v>5.39</v>
+        <v>2.5299999999999998</v>
       </c>
       <c r="H39" s="9">
         <v>0</v>
@@ -3239,25 +3239,25 @@
     </row>
     <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
-        <v>43617</v>
+        <v>43647</v>
       </c>
       <c r="B40" s="7">
-        <v>20.5</v>
+        <v>20.22</v>
       </c>
       <c r="C40" s="7">
-        <v>20.22</v>
+        <v>21.31</v>
       </c>
       <c r="D40" s="7">
-        <v>21.99</v>
+        <v>24</v>
       </c>
       <c r="E40" s="7">
-        <v>20</v>
-      </c>
-      <c r="F40" s="8">
-        <v>-0.28000000000000003</v>
-      </c>
-      <c r="G40" s="8">
-        <v>-1.37</v>
+        <v>20.010000000000002</v>
+      </c>
+      <c r="F40" s="10">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="G40" s="10">
+        <v>5.39</v>
       </c>
       <c r="H40" s="9">
         <v>0</v>
@@ -3292,25 +3292,25 @@
     </row>
     <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
-        <v>43586</v>
+        <v>43617</v>
       </c>
       <c r="B41" s="7">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="C41" s="7">
-        <v>20.5</v>
+        <v>20.22</v>
       </c>
       <c r="D41" s="7">
-        <v>22.09</v>
+        <v>21.99</v>
       </c>
       <c r="E41" s="7">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="F41" s="8">
-        <v>-1</v>
+        <v>-0.28000000000000003</v>
       </c>
       <c r="G41" s="8">
-        <v>-4.6500000000000004</v>
+        <v>-1.37</v>
       </c>
       <c r="H41" s="9">
         <v>0</v>
@@ -3345,25 +3345,25 @@
     </row>
     <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
-        <v>43556</v>
+        <v>43586</v>
       </c>
       <c r="B42" s="7">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="C42" s="7">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="D42" s="7">
-        <v>23</v>
+        <v>22.09</v>
       </c>
       <c r="E42" s="7">
-        <v>17.420000000000002</v>
-      </c>
-      <c r="F42" s="10">
-        <v>1.8</v>
-      </c>
-      <c r="G42" s="10">
-        <v>9.14</v>
+        <v>19.5</v>
+      </c>
+      <c r="F42" s="8">
+        <v>-1</v>
+      </c>
+      <c r="G42" s="8">
+        <v>-4.6500000000000004</v>
       </c>
       <c r="H42" s="9">
         <v>0</v>
@@ -3398,25 +3398,25 @@
     </row>
     <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
-        <v>43525</v>
+        <v>43556</v>
       </c>
       <c r="B43" s="7">
-        <v>22.5</v>
+        <v>19.7</v>
       </c>
       <c r="C43" s="7">
-        <v>19.7</v>
+        <v>21.5</v>
       </c>
       <c r="D43" s="7">
-        <v>22.5</v>
+        <v>23</v>
       </c>
       <c r="E43" s="7">
-        <v>14.5</v>
-      </c>
-      <c r="F43" s="8">
-        <v>-2.8</v>
-      </c>
-      <c r="G43" s="8">
-        <v>-12.44</v>
+        <v>17.420000000000002</v>
+      </c>
+      <c r="F43" s="10">
+        <v>1.8</v>
+      </c>
+      <c r="G43" s="10">
+        <v>9.14</v>
       </c>
       <c r="H43" s="9">
         <v>0</v>
@@ -3451,25 +3451,25 @@
     </row>
     <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
-        <v>43497</v>
+        <v>43525</v>
       </c>
       <c r="B44" s="7">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="C44" s="7">
+        <v>19.7</v>
+      </c>
+      <c r="D44" s="7">
         <v>22.5</v>
       </c>
-      <c r="D44" s="7">
-        <v>24.84</v>
-      </c>
       <c r="E44" s="7">
-        <v>22.21</v>
+        <v>14.5</v>
       </c>
       <c r="F44" s="8">
-        <v>-1.71</v>
+        <v>-2.8</v>
       </c>
       <c r="G44" s="8">
-        <v>-7.06</v>
+        <v>-12.44</v>
       </c>
       <c r="H44" s="9">
         <v>0</v>
@@ -3477,8 +3477,8 @@
       <c r="I44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J44" s="8">
-        <v>-100</v>
+      <c r="J44" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="9">
         <v>0</v>
@@ -3492,8 +3492,8 @@
       <c r="N44" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O44" s="8">
-        <v>-100</v>
+      <c r="O44" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P44" s="9">
         <v>0</v>
@@ -3504,25 +3504,25 @@
     </row>
     <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
-        <v>43466</v>
+        <v>43497</v>
       </c>
       <c r="B45" s="7">
-        <v>27.02</v>
+        <v>24.21</v>
       </c>
       <c r="C45" s="7">
-        <v>24.21</v>
+        <v>22.5</v>
       </c>
       <c r="D45" s="7">
-        <v>27.02</v>
+        <v>24.84</v>
       </c>
       <c r="E45" s="7">
-        <v>23.58</v>
+        <v>22.21</v>
       </c>
       <c r="F45" s="8">
-        <v>-2.81</v>
+        <v>-1.71</v>
       </c>
       <c r="G45" s="8">
-        <v>-10.4</v>
+        <v>-7.06</v>
       </c>
       <c r="H45" s="9">
         <v>0</v>
@@ -3530,14 +3530,14 @@
       <c r="I45" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J45" s="9" t="s">
-        <v>17</v>
+      <c r="J45" s="8">
+        <v>-100</v>
       </c>
       <c r="K45" s="9">
         <v>0</v>
       </c>
-      <c r="L45" s="9" t="s">
-        <v>17</v>
+      <c r="L45" s="8">
+        <v>-100</v>
       </c>
       <c r="M45" s="9">
         <v>0</v>
@@ -3545,37 +3545,37 @@
       <c r="N45" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O45" s="9" t="s">
-        <v>17</v>
+      <c r="O45" s="8">
+        <v>-100</v>
       </c>
       <c r="P45" s="9">
         <v>0</v>
       </c>
-      <c r="Q45" s="9" t="s">
-        <v>17</v>
+      <c r="Q45" s="8">
+        <v>-100</v>
       </c>
     </row>
     <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
-        <v>43435</v>
+        <v>43466</v>
       </c>
       <c r="B46" s="7">
-        <v>28.99</v>
+        <v>27.02</v>
       </c>
       <c r="C46" s="7">
+        <v>24.21</v>
+      </c>
+      <c r="D46" s="7">
         <v>27.02</v>
       </c>
-      <c r="D46" s="7">
-        <v>30.3</v>
-      </c>
       <c r="E46" s="7">
-        <v>26.81</v>
+        <v>23.58</v>
       </c>
       <c r="F46" s="8">
-        <v>-1.97</v>
+        <v>-2.81</v>
       </c>
       <c r="G46" s="8">
-        <v>-6.8</v>
+        <v>-10.4</v>
       </c>
       <c r="H46" s="9">
         <v>0</v>
@@ -3587,10 +3587,10 @@
         <v>17</v>
       </c>
       <c r="K46" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="L46" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="L46" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="M46" s="9">
         <v>0</v>
@@ -3602,33 +3602,33 @@
         <v>17</v>
       </c>
       <c r="P46" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="Q46" s="9">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q46" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
-        <v>43405</v>
+        <v>43435</v>
       </c>
       <c r="B47" s="7">
-        <v>28.93</v>
+        <v>28.99</v>
       </c>
       <c r="C47" s="7">
-        <v>28.99</v>
+        <v>27.02</v>
       </c>
       <c r="D47" s="7">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="E47" s="7">
-        <v>27.5</v>
-      </c>
-      <c r="F47" s="10">
-        <v>0.06</v>
-      </c>
-      <c r="G47" s="10">
-        <v>0.21</v>
+        <v>26.81</v>
+      </c>
+      <c r="F47" s="8">
+        <v>-1.97</v>
+      </c>
+      <c r="G47" s="8">
+        <v>-6.8</v>
       </c>
       <c r="H47" s="9">
         <v>0</v>
@@ -3663,25 +3663,25 @@
     </row>
     <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
-        <v>43374</v>
+        <v>43405</v>
       </c>
       <c r="B48" s="7">
-        <v>31.99</v>
+        <v>28.93</v>
       </c>
       <c r="C48" s="7">
-        <v>28.93</v>
+        <v>28.99</v>
       </c>
       <c r="D48" s="7">
-        <v>31.49</v>
+        <v>30</v>
       </c>
       <c r="E48" s="7">
-        <v>26.71</v>
-      </c>
-      <c r="F48" s="8">
-        <v>-3.06</v>
-      </c>
-      <c r="G48" s="8">
-        <v>-9.57</v>
+        <v>27.5</v>
+      </c>
+      <c r="F48" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="G48" s="10">
+        <v>0.21</v>
       </c>
       <c r="H48" s="9">
         <v>0</v>
@@ -3716,25 +3716,25 @@
     </row>
     <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
-        <v>43344</v>
+        <v>43374</v>
       </c>
       <c r="B49" s="7">
-        <v>38.01</v>
+        <v>31.99</v>
       </c>
       <c r="C49" s="7">
-        <v>31.99</v>
+        <v>28.93</v>
       </c>
       <c r="D49" s="7">
-        <v>38.979999999999997</v>
+        <v>31.49</v>
       </c>
       <c r="E49" s="7">
-        <v>28.5</v>
+        <v>26.71</v>
       </c>
       <c r="F49" s="8">
-        <v>-6.02</v>
+        <v>-3.06</v>
       </c>
       <c r="G49" s="8">
-        <v>-15.84</v>
+        <v>-9.57</v>
       </c>
       <c r="H49" s="9">
         <v>0</v>
@@ -3769,25 +3769,25 @@
     </row>
     <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
-        <v>43313</v>
+        <v>43344</v>
       </c>
       <c r="B50" s="7">
-        <v>43.39</v>
+        <v>38.01</v>
       </c>
       <c r="C50" s="7">
-        <v>38.01</v>
+        <v>31.99</v>
       </c>
       <c r="D50" s="7">
-        <v>54</v>
+        <v>38.979999999999997</v>
       </c>
       <c r="E50" s="7">
-        <v>35.6</v>
+        <v>28.5</v>
       </c>
       <c r="F50" s="8">
-        <v>-6.38</v>
+        <v>-6.02</v>
       </c>
       <c r="G50" s="8">
-        <v>-14.37</v>
+        <v>-15.84</v>
       </c>
       <c r="H50" s="9">
         <v>0</v>
@@ -3795,8 +3795,8 @@
       <c r="I50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J50" s="8">
-        <v>-100</v>
+      <c r="J50" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="K50" s="9">
         <v>6.8999999999999999E-3</v>
@@ -3810,8 +3810,8 @@
       <c r="N50" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O50" s="8">
-        <v>-100</v>
+      <c r="O50" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="P50" s="9">
         <v>6.8999999999999999E-3</v>
@@ -3822,25 +3822,25 @@
     </row>
     <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
-        <v>43282</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G51" s="9" t="s">
-        <v>17</v>
+        <v>43313</v>
+      </c>
+      <c r="B51" s="7">
+        <v>43.39</v>
+      </c>
+      <c r="C51" s="7">
+        <v>38.01</v>
+      </c>
+      <c r="D51" s="7">
+        <v>54</v>
+      </c>
+      <c r="E51" s="7">
+        <v>35.6</v>
+      </c>
+      <c r="F51" s="8">
+        <v>-6.38</v>
+      </c>
+      <c r="G51" s="8">
+        <v>-14.37</v>
       </c>
       <c r="H51" s="9">
         <v>0</v>
@@ -3848,14 +3848,14 @@
       <c r="I51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J51" s="9" t="s">
-        <v>17</v>
+      <c r="J51" s="8">
+        <v>-100</v>
       </c>
       <c r="K51" s="9">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="L51" s="9" t="s">
-        <v>17</v>
+      <c r="L51" s="9">
+        <v>0</v>
       </c>
       <c r="M51" s="9">
         <v>0</v>
@@ -3863,19 +3863,19 @@
       <c r="N51" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O51" s="9" t="s">
-        <v>17</v>
+      <c r="O51" s="8">
+        <v>-100</v>
       </c>
       <c r="P51" s="9">
         <v>6.8999999999999999E-3</v>
       </c>
-      <c r="Q51" s="9" t="s">
-        <v>17</v>
+      <c r="Q51" s="9">
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
-        <v>43252</v>
+        <v>43282</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>17</v>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
-        <v>43221</v>
+        <v>43252</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>17</v>
@@ -3981,7 +3981,7 @@
     </row>
     <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
-        <v>43191</v>
+        <v>43221</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>17</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
-        <v>43160</v>
+        <v>43191</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>17</v>
@@ -4057,8 +4057,8 @@
       <c r="H55" s="9">
         <v>0</v>
       </c>
-      <c r="I55" s="8">
-        <v>-100</v>
+      <c r="I55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>17</v>
@@ -4072,8 +4072,8 @@
       <c r="M55" s="9">
         <v>0</v>
       </c>
-      <c r="N55" s="8">
-        <v>-100</v>
+      <c r="N55" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>17</v>
@@ -4087,7 +4087,7 @@
     </row>
     <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
-        <v>43132</v>
+        <v>43160</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>17</v>
@@ -4108,10 +4108,10 @@
         <v>17</v>
       </c>
       <c r="H56" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="I56" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I56" s="8">
+        <v>-100</v>
       </c>
       <c r="J56" s="9" t="s">
         <v>17</v>
@@ -4123,10 +4123,10 @@
         <v>17</v>
       </c>
       <c r="M56" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="N56" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N56" s="8">
+        <v>-100</v>
       </c>
       <c r="O56" s="9" t="s">
         <v>17</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
-        <v>43101</v>
+        <v>43132</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>17</v>
@@ -4161,7 +4161,7 @@
         <v>17</v>
       </c>
       <c r="H57" s="9">
-        <v>0</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="I57" s="9" t="s">
         <v>17</v>
@@ -4170,13 +4170,13 @@
         <v>17</v>
       </c>
       <c r="K57" s="9">
-        <v>0</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="L57" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M57" s="9">
-        <v>0</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="N57" s="9" t="s">
         <v>17</v>
@@ -4185,7 +4185,7 @@
         <v>17</v>
       </c>
       <c r="P57" s="9">
-        <v>0</v>
+        <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q57" s="9" t="s">
         <v>17</v>
@@ -4193,7 +4193,7 @@
     </row>
     <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
-        <v>43070</v>
+        <v>43101</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>17</v>
@@ -4223,7 +4223,7 @@
         <v>17</v>
       </c>
       <c r="K58" s="9">
-        <v>6.8999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="L58" s="9" t="s">
         <v>17</v>
@@ -4238,7 +4238,7 @@
         <v>17</v>
       </c>
       <c r="P58" s="9">
-        <v>6.8999999999999999E-3</v>
+        <v>0</v>
       </c>
       <c r="Q58" s="9" t="s">
         <v>17</v>
@@ -4246,7 +4246,7 @@
     </row>
     <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
-        <v>43040</v>
+        <v>43070</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>17</v>
@@ -4299,7 +4299,7 @@
     </row>
     <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
-        <v>43009</v>
+        <v>43040</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>17</v>
@@ -4352,7 +4352,7 @@
     </row>
     <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
-        <v>42979</v>
+        <v>43009</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>17</v>
@@ -4375,8 +4375,8 @@
       <c r="H61" s="9">
         <v>0</v>
       </c>
-      <c r="I61" s="8">
-        <v>-100</v>
+      <c r="I61" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>17</v>
@@ -4390,8 +4390,8 @@
       <c r="M61" s="9">
         <v>0</v>
       </c>
-      <c r="N61" s="8">
-        <v>-100</v>
+      <c r="N61" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>17</v>
@@ -4405,7 +4405,7 @@
     </row>
     <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
-        <v>42948</v>
+        <v>42979</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>17</v>
@@ -4426,10 +4426,10 @@
         <v>17</v>
       </c>
       <c r="H62" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="I62" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="I62" s="8">
+        <v>-100</v>
       </c>
       <c r="J62" s="9" t="s">
         <v>17</v>
@@ -4441,10 +4441,10 @@
         <v>17</v>
       </c>
       <c r="M62" s="9">
-        <v>6.8999999999999999E-3</v>
-      </c>
-      <c r="N62" s="9" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="N62" s="8">
+        <v>-100</v>
       </c>
       <c r="O62" s="9" t="s">
         <v>17</v>
@@ -4453,6 +4453,59 @@
         <v>6.8999999999999999E-3</v>
       </c>
       <c r="Q62" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>42948</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63" s="9">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="I63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="9">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="L63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M63" s="9">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="N63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O63" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P63" s="9">
+        <v>6.8999999999999999E-3</v>
+      </c>
+      <c r="Q63" s="9" t="s">
         <v>17</v>
       </c>
     </row>
